--- a/mcmods.xlsx
+++ b/mcmods.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
   <si>
     <t>Wichtig?</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>continuity</t>
+  </si>
+  <si>
+    <t>nicht mehr benötigt</t>
   </si>
 </sst>
 </file>
@@ -201,7 +204,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -229,6 +232,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor rgb="FF993300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor rgb="FFC55A11"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor rgb="FF993300"/>
       </patternFill>
     </fill>
@@ -260,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -277,6 +292,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -628,6 +645,9 @@
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
+      <c r="I7" s="12" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
@@ -836,7 +856,7 @@
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
+      <c r="G24" s="13"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>

--- a/mcmods.xlsx
+++ b/mcmods.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max.DESKTOP-8EH97AE\Documents\Minecraft\MC-Mods\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max.DESKTOP-8EH97AE\Documents\Spiele\Minecraft\MC-Mods\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="46">
   <si>
     <t>Wichtig?</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t>nicht mehr benötigt</t>
+  </si>
+  <si>
+    <t>*26.1.1</t>
   </si>
 </sst>
 </file>
@@ -204,7 +207,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -244,6 +247,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor rgb="FF993300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor rgb="FF339966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor rgb="FF339966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor rgb="FF339966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor rgb="FF993300"/>
       </patternFill>
     </fill>
@@ -275,7 +302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -294,6 +321,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -555,15 +587,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:I67"/>
+  <dimension ref="A3:J67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
-    <col min="9" max="9" width="27" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -585,11 +618,14 @@
       <c r="G3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="H3" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
@@ -601,11 +637,12 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
-      <c r="I4" s="7" t="s">
+      <c r="H4" s="14"/>
+      <c r="J4" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -617,11 +654,12 @@
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="11"/>
-      <c r="I5" s="8" t="s">
+      <c r="H5" s="8"/>
+      <c r="J5" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
         <v>37</v>
@@ -631,11 +669,12 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
-      <c r="I6" s="9" t="s">
+      <c r="H6" s="7"/>
+      <c r="J6" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
         <v>13</v>
@@ -645,11 +684,12 @@
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
-      <c r="I7" s="12" t="s">
+      <c r="H7" s="7"/>
+      <c r="J7" s="12" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -661,8 +701,9 @@
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
         <v>16</v>
@@ -672,8 +713,9 @@
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
@@ -685,8 +727,9 @@
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
-    </row>
-    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="6" t="s">
         <v>43</v>
@@ -696,8 +739,9 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
-    </row>
-    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
@@ -709,8 +753,9 @@
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
-    </row>
-    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="6" t="s">
         <v>38</v>
@@ -720,8 +765,9 @@
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>8</v>
       </c>
@@ -733,8 +779,9 @@
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>8</v>
       </c>
@@ -746,8 +793,9 @@
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>8</v>
       </c>
@@ -759,8 +807,9 @@
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>8</v>
       </c>
@@ -772,8 +821,9 @@
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>8</v>
       </c>
@@ -785,8 +835,9 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="6" t="s">
         <v>22</v>
@@ -796,8 +847,9 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H19" s="16"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>8</v>
       </c>
@@ -809,8 +861,9 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>8</v>
       </c>
@@ -822,8 +875,9 @@
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H21" s="7"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>8</v>
       </c>
@@ -835,8 +889,9 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H22" s="7"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="6" t="s">
         <v>26</v>
@@ -846,8 +901,9 @@
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H23" s="17"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="6" t="s">
         <v>27</v>
@@ -857,8 +913,9 @@
       <c r="E24" s="7"/>
       <c r="F24" s="8"/>
       <c r="G24" s="13"/>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H24" s="18"/>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="6" t="s">
         <v>41</v>
@@ -868,8 +925,9 @@
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H25" s="7"/>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="6" t="s">
         <v>42</v>
@@ -879,8 +937,9 @@
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H26" s="7"/>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>8</v>
       </c>
@@ -892,8 +951,9 @@
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H27" s="7"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>8</v>
       </c>
@@ -905,8 +965,9 @@
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H28" s="7"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>8</v>
       </c>
@@ -918,8 +979,9 @@
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H29" s="7"/>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="B30" s="6" t="s">
         <v>31</v>
@@ -929,8 +991,9 @@
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H30" s="14"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="6" t="s">
         <v>32</v>
@@ -940,8 +1003,9 @@
       <c r="E31" s="10"/>
       <c r="F31" s="7"/>
       <c r="G31" s="11"/>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H31" s="11"/>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>8</v>
       </c>
@@ -953,8 +1017,9 @@
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H32" s="14"/>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>8</v>
       </c>
@@ -966,8 +1031,9 @@
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H33" s="14"/>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>8</v>
       </c>
@@ -979,8 +1045,9 @@
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H34" s="7"/>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>8</v>
       </c>
@@ -992,6 +1059,7 @@
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
     </row>
     <row r="67" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C67">

--- a/mcmods.xlsx
+++ b/mcmods.xlsx
@@ -161,7 +161,7 @@
     <t>nicht mehr benötigt</t>
   </si>
   <si>
-    <t>*26.1.1</t>
+    <t>*26.1.2</t>
   </si>
 </sst>
 </file>
@@ -207,7 +207,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -264,12 +264,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="-0.249977111117893"/>
-        <bgColor rgb="FF339966"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor rgb="FF993300"/>
       </patternFill>
@@ -302,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -325,7 +319,6 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -654,7 +647,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="11"/>
-      <c r="H5" s="8"/>
+      <c r="H5" s="11"/>
       <c r="J5" s="8" t="s">
         <v>12</v>
       </c>
@@ -901,7 +894,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="17"/>
+      <c r="H23" s="7"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
@@ -913,7 +906,7 @@
       <c r="E24" s="7"/>
       <c r="F24" s="8"/>
       <c r="G24" s="13"/>
-      <c r="H24" s="18"/>
+      <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
@@ -991,7 +984,7 @@
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
-      <c r="H30" s="14"/>
+      <c r="H30" s="7"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
@@ -1017,7 +1010,7 @@
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
-      <c r="H32" s="14"/>
+      <c r="H32" s="7"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
@@ -1031,7 +1024,7 @@
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
-      <c r="H33" s="14"/>
+      <c r="H33" s="7"/>
     </row>
     <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">

--- a/mcmods.xlsx
+++ b/mcmods.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
   <si>
     <t>Wichtig?</t>
   </si>
@@ -146,9 +146,6 @@
     <t>immediatly fast</t>
   </si>
   <si>
-    <t>ferritcore</t>
-  </si>
-  <si>
     <t>shulkerbox tooltip</t>
   </si>
   <si>
@@ -162,13 +159,19 @@
   </si>
   <si>
     <t>*26.1.2</t>
+  </si>
+  <si>
+    <t>*26.2</t>
+  </si>
+  <si>
+    <t>ferritecore</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -206,8 +209,15 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -248,12 +258,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor rgb="FF993300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.249977111117893"/>
-        <bgColor rgb="FF339966"/>
       </patternFill>
     </fill>
     <fill>
@@ -315,10 +319,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -580,16 +584,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:J67"/>
+  <dimension ref="A3:N67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" customWidth="1"/>
+    <col min="14" max="14" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -611,14 +616,17 @@
       <c r="G3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
@@ -630,12 +638,13 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="14"/>
-      <c r="J4" s="7" t="s">
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="N4" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -648,11 +657,12 @@
       <c r="F5" s="7"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
-      <c r="J5" s="8" t="s">
+      <c r="I5" s="8"/>
+      <c r="N5" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
         <v>37</v>
@@ -663,11 +673,12 @@
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
-      <c r="J6" s="9" t="s">
+      <c r="I6" s="7"/>
+      <c r="N6" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
         <v>13</v>
@@ -678,11 +689,12 @@
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
-      <c r="J7" s="12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I7" s="7"/>
+      <c r="N7" s="12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -695,8 +707,9 @@
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
         <v>16</v>
@@ -707,8 +720,9 @@
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
-    </row>
-    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I9" s="8"/>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
@@ -721,11 +735,12 @@
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -733,8 +748,9 @@
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
@@ -747,8 +763,9 @@
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="6" t="s">
         <v>38</v>
@@ -759,8 +776,9 @@
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>8</v>
       </c>
@@ -773,8 +791,9 @@
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>8</v>
       </c>
@@ -787,13 +806,14 @@
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -801,8 +821,9 @@
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>8</v>
       </c>
@@ -815,8 +836,9 @@
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>8</v>
       </c>
@@ -829,8 +851,9 @@
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="6" t="s">
         <v>22</v>
@@ -840,9 +863,10 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
-      <c r="H19" s="16"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>8</v>
       </c>
@@ -855,8 +879,9 @@
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I20" s="7"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>8</v>
       </c>
@@ -869,8 +894,9 @@
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>8</v>
       </c>
@@ -883,8 +909,9 @@
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="6" t="s">
         <v>26</v>
@@ -895,8 +922,9 @@
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="6" t="s">
         <v>27</v>
@@ -906,12 +934,13 @@
       <c r="E24" s="7"/>
       <c r="F24" s="8"/>
       <c r="G24" s="13"/>
-      <c r="H24" s="17"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -919,11 +948,12 @@
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I25" s="7"/>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
@@ -931,8 +961,9 @@
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I26" s="7"/>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>8</v>
       </c>
@@ -945,8 +976,9 @@
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I27" s="7"/>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>8</v>
       </c>
@@ -959,8 +991,9 @@
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I28" s="7"/>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>8</v>
       </c>
@@ -973,8 +1006,9 @@
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I29" s="7"/>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="B30" s="6" t="s">
         <v>31</v>
@@ -985,8 +1019,9 @@
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I30" s="7"/>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="6" t="s">
         <v>32</v>
@@ -997,8 +1032,9 @@
       <c r="F31" s="7"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
-    </row>
-    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I31" s="11"/>
+    </row>
+    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>8</v>
       </c>
@@ -1011,8 +1047,9 @@
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I32" s="7"/>
+    </row>
+    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>8</v>
       </c>
@@ -1025,8 +1062,9 @@
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I33" s="7"/>
+    </row>
+    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>8</v>
       </c>
@@ -1039,8 +1077,9 @@
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I34" s="7"/>
+    </row>
+    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>8</v>
       </c>
@@ -1053,6 +1092,7 @@
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
     </row>
     <row r="67" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C67">

--- a/mcmods.xlsx
+++ b/mcmods.xlsx
@@ -1,20 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max.DESKTOP-8EH97AE\Documents\Spiele\Minecraft\MC-Mods\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="6"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tabelle1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -26,152 +22,157 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
   <si>
-    <t>Wichtig?</t>
-  </si>
-  <si>
-    <t>Mods</t>
-  </si>
-  <si>
-    <t>1.20.4</t>
-  </si>
-  <si>
-    <t>1.21.0</t>
-  </si>
-  <si>
-    <t>1.21.4</t>
-  </si>
-  <si>
-    <t>1.21.10</t>
-  </si>
-  <si>
-    <t>1.21.11</t>
-  </si>
-  <si>
-    <t>Legende</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>architectury</t>
-  </si>
-  <si>
-    <t>verfügbar</t>
-  </si>
-  <si>
-    <t>betterf3</t>
-  </si>
-  <si>
-    <t>nicht verfügbar</t>
-  </si>
-  <si>
-    <t>blur</t>
-  </si>
-  <si>
-    <t>hoffentlich funktionstüchtig</t>
-  </si>
-  <si>
-    <t>bobby</t>
-  </si>
-  <si>
-    <t>citresewn</t>
-  </si>
-  <si>
-    <t>clothconfig</t>
-  </si>
-  <si>
-    <t>dynamicfps</t>
-  </si>
-  <si>
-    <t>fabric api</t>
-  </si>
-  <si>
-    <t>fabric language kotlin</t>
-  </si>
-  <si>
-    <t>iris</t>
-  </si>
-  <si>
-    <t>jei</t>
-  </si>
-  <si>
-    <t>lambdynamiclights</t>
-  </si>
-  <si>
-    <t>lithium</t>
-  </si>
-  <si>
-    <t>modmenu</t>
-  </si>
-  <si>
-    <t>mousewheelie</t>
-  </si>
-  <si>
-    <t>musiccontrol</t>
-  </si>
-  <si>
-    <t>sodiumfabric</t>
-  </si>
-  <si>
-    <t>soundphysicsremastered</t>
-  </si>
-  <si>
-    <t>viafabric</t>
-  </si>
-  <si>
-    <t>worldedit</t>
-  </si>
-  <si>
-    <t>worldeditcui</t>
-  </si>
-  <si>
-    <t>xaeros minimap</t>
-  </si>
-  <si>
-    <t>xaeros wolrdmap</t>
-  </si>
-  <si>
-    <t>yetanotherconfiglib</t>
-  </si>
-  <si>
-    <t>zoomify</t>
-  </si>
-  <si>
-    <t>bettermountHUD</t>
-  </si>
-  <si>
-    <t>entity culling</t>
-  </si>
-  <si>
-    <t>immediatly fast</t>
-  </si>
-  <si>
-    <t>shulkerbox tooltip</t>
-  </si>
-  <si>
-    <t>skinlayers 3d</t>
-  </si>
-  <si>
-    <t>continuity</t>
-  </si>
-  <si>
-    <t>nicht mehr benötigt</t>
-  </si>
-  <si>
-    <t>*26.1.2</t>
-  </si>
-  <si>
-    <t>*26.2</t>
-  </si>
-  <si>
-    <t>ferritecore</t>
+    <t xml:space="preserve">Wichtig?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*26.1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*26.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legende</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">architectury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verfügbar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">betterf3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nicht verfügbar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bettermountHUD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hoffentlich funktionstüchtig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nicht mehr benötigt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bobby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">citresewn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clothconfig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">continuity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dynamicfps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">entity culling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fabric api</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fabric language kotlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ferritecore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immediatly fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lambdynamiclights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lithium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">modmenu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mousewheelie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">musiccontrol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shulkerbox tooltip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skinlayers 3d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sodiumfabric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soundphysicsremastered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">viafabric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">worldedit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">worldeditcui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xaeros minimap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xaeros wolrdmap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yetanotherconfiglib</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zoomify</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="mmm\ yy"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+  </numFmts>
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,7 +181,22 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -188,7 +204,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -204,20 +220,20 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="9"/>
+      <color theme="0" tint="-0.5"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.499984740745262"/>
+      <color theme="9"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -226,109 +242,146 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
-        <bgColor rgb="FF339966"/>
+        <fgColor theme="9" tint="-0.25"/>
+        <bgColor rgb="FF808080"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.249977111117893"/>
+        <fgColor theme="0" tint="-0.35"/>
+        <bgColor rgb="FFBFBFBF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.25"/>
         <bgColor rgb="FF993300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="-0.249977111117893"/>
+        <fgColor theme="7" tint="-0.25"/>
         <bgColor rgb="FFC55A11"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
-        <bgColor rgb="FF993300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor rgb="FFC55A11"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor rgb="FF993300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
-        <bgColor rgb="FF339966"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
-        <bgColor rgb="FF993300"/>
+        <fgColor theme="0" tint="-0.25"/>
+        <bgColor rgb="FFCCCCFF"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellXfs count="15">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -345,7 +398,7 @@
       <rgbColor rgb="FF548235"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFBFBFBF"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -378,38 +431,22 @@
       <rgbColor rgb="FFBF9000"/>
       <rgbColor rgb="FFC55A11"/>
       <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FFA6A6A6"/>
+      <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF70AD47"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -451,12 +488,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -488,7 +525,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -512,7 +549,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -572,29 +609,29 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A3:N67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="10.140625" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" customWidth="1"/>
-    <col min="14" max="14" width="29" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="29"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -616,56 +653,56 @@
       <c r="G3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="N3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
       <c r="N4" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="8"/>
-      <c r="N5" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="N5" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -674,14 +711,14 @@
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
-      <c r="N6" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="N6" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -690,16 +727,16 @@
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
-      <c r="N7" s="12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="N7" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -709,25 +746,25 @@
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
     </row>
-    <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-    </row>
-    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -737,10 +774,10 @@
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
     </row>
-    <row r="11" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
       <c r="B11" s="6" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -750,12 +787,12 @@
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
     </row>
-    <row r="12" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -765,10 +802,10 @@
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
     </row>
-    <row r="13" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
       <c r="B13" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -778,12 +815,12 @@
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
     </row>
-    <row r="14" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -793,12 +830,12 @@
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
     </row>
-    <row r="15" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -808,12 +845,12 @@
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
     </row>
-    <row r="16" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -823,12 +860,12 @@
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
     </row>
-    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -838,12 +875,12 @@
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
     </row>
-    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
@@ -853,25 +890,25 @@
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
     </row>
-    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
       <c r="B19" s="6" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-    </row>
-    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
@@ -881,12 +918,12 @@
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
     </row>
-    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
@@ -896,12 +933,12 @@
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
     </row>
-    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
@@ -911,10 +948,10 @@
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
     </row>
-    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
       <c r="B23" s="6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -924,23 +961,23 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
     </row>
-    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
       <c r="B24" s="6" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="8"/>
+      <c r="F24" s="9"/>
       <c r="G24" s="13"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-    </row>
-    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5"/>
       <c r="B25" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -950,10 +987,10 @@
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
     </row>
-    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
       <c r="B26" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
@@ -963,12 +1000,12 @@
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
     </row>
-    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
@@ -978,12 +1015,12 @@
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
     </row>
-    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -993,12 +1030,12 @@
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
     </row>
-    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -1008,10 +1045,10 @@
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
     </row>
-    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
       <c r="B30" s="6" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -1021,25 +1058,25 @@
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
     </row>
-    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
       <c r="B31" s="6" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
-      <c r="E31" s="10"/>
+      <c r="E31" s="14"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-    </row>
-    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -1049,12 +1086,12 @@
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
     </row>
-    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -1064,12 +1101,12 @@
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
     </row>
-    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -1079,12 +1116,12 @@
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
     </row>
-    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -1094,14 +1131,19 @@
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
     </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C67">
-        <f>SUM(C42:C57)</f>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C67" s="0" t="n">
+        <f aca="false">SUM(C42:C57)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/mcmods.xlsx
+++ b/mcmods.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="48">
   <si>
     <t xml:space="preserve">Wichtig?</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t xml:space="preserve">*26.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*26.3</t>
   </si>
   <si>
     <t xml:space="preserve">Legende</t>
@@ -254,7 +257,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.25"/>
+        <fgColor rgb="FFC55A11"/>
         <bgColor rgb="FF993300"/>
       </patternFill>
     </fill>
@@ -312,64 +315,72 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -625,514 +636,549 @@
   <dimension ref="A3:N67"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="29"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="J3" s="5" t="s">
         <v>9</v>
       </c>
+      <c r="N3" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="N4" s="7" t="s">
+      <c r="A4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>12</v>
       </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="N4" s="8" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="N5" s="9" t="s">
+      <c r="A5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="10"/>
+      <c r="N5" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="N6" s="10" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="7" t="s">
         <v>16</v>
       </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="10"/>
+      <c r="N6" s="12" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="N7" s="11" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7" t="s">
         <v>18</v>
       </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="10"/>
+      <c r="N7" s="13" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
+      <c r="A8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
+      <c r="A10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
+      <c r="A12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
+      <c r="A14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
+      <c r="A15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
+      <c r="A16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
+      <c r="A17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
+      <c r="A18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
+      <c r="A20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
+      <c r="A21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
+      <c r="A22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5"/>
-      <c r="B23" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
+      <c r="A26" s="6"/>
+      <c r="B26" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
+      <c r="A27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
+      <c r="A28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
+      <c r="A29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
+      <c r="A30" s="6"/>
+      <c r="B30" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5"/>
-      <c r="B31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
+      <c r="A32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
+      <c r="A33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
+      <c r="A34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
+      <c r="A35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C67" s="0" t="n">
+      <c r="C67" s="1" t="n">
         <f aca="false">SUM(C42:C57)</f>
         <v>0</v>
       </c>

--- a/mcmods.xlsx
+++ b/mcmods.xlsx
@@ -744,7 +744,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="10"/>
+      <c r="J7" s="8"/>
       <c r="N7" s="13" t="s">
         <v>19</v>
       </c>
@@ -837,7 +837,7 @@
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
-      <c r="J13" s="10"/>
+      <c r="J13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">

--- a/mcmods.xlsx
+++ b/mcmods.xlsx
@@ -356,27 +356,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -710,8 +710,8 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="10"/>
-      <c r="N5" s="11" t="s">
+      <c r="J5" s="8"/>
+      <c r="N5" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -727,8 +727,8 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
-      <c r="J6" s="10"/>
-      <c r="N6" s="12" t="s">
+      <c r="J6" s="8"/>
+      <c r="N6" s="11" t="s">
         <v>17</v>
       </c>
     </row>
@@ -745,7 +745,7 @@
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="N7" s="13" t="s">
+      <c r="N7" s="12" t="s">
         <v>19</v>
       </c>
     </row>
@@ -763,7 +763,7 @@
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
-      <c r="J8" s="10"/>
+      <c r="J8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
@@ -772,12 +772,12 @@
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
@@ -993,7 +993,7 @@
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
-      <c r="J23" s="10"/>
+      <c r="J23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6"/>
@@ -1003,8 +1003,8 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="15"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="14"/>
       <c r="H24" s="14"/>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
@@ -1097,7 +1097,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
-      <c r="J30" s="10"/>
+      <c r="J30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6"/>
@@ -1111,7 +1111,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
-      <c r="J31" s="10"/>
+      <c r="J31" s="8"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
@@ -1175,7 +1175,7 @@
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
-      <c r="J35" s="10"/>
+      <c r="J35" s="8"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C67" s="1" t="n">

--- a/mcmods.xlsx
+++ b/mcmods.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
   <si>
     <t xml:space="preserve">Wichtig?</t>
   </si>
@@ -122,6 +122,12 @@
   </si>
   <si>
     <t xml:space="preserve">lithium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">malilib</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minihud</t>
   </si>
   <si>
     <t xml:space="preserve">modmenu</t>
@@ -634,7 +640,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A3:N67"/>
-  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.71"/>
@@ -993,7 +999,7 @@
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
-      <c r="J23" s="15"/>
+      <c r="J23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6"/>
@@ -1003,11 +1009,11 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6"/>
@@ -1021,7 +1027,7 @@
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
+      <c r="J25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
@@ -1031,11 +1037,11 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
@@ -1106,7 +1112,7 @@
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
-      <c r="E31" s="16"/>
+      <c r="E31" s="8"/>
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
@@ -1138,7 +1144,7 @@
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
+      <c r="E33" s="16"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
@@ -1176,6 +1182,32 @@
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
       <c r="J35" s="8"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C67" s="1" t="n">
